--- a/MSC_mean_lt.xlsx
+++ b/MSC_mean_lt.xlsx
@@ -69,7 +69,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C569"/>
+  <dimension ref="A1:C577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1439,7 +1439,7 @@
         <v>33390</v>
       </c>
       <c r="B163" s="2">
-        <v>4.5956989247311819</v>
+        <v>4.5922746781116022</v>
       </c>
       <c r="C163" s="2">
         <v>4</v>
@@ -5784,7 +5784,7 @@
         <v>45413</v>
       </c>
       <c r="B558" s="2">
-        <v>3.7880288799056112</v>
+        <v>3.6026375477038712</v>
       </c>
       <c r="C558" s="2">
         <v>3</v>
@@ -5795,7 +5795,7 @@
         <v>45444</v>
       </c>
       <c r="B559" s="2">
-        <v>3.7689617781435949</v>
+        <v>3.8348921734169981</v>
       </c>
       <c r="C559" s="2">
         <v>3</v>
@@ -5839,7 +5839,7 @@
         <v>45566</v>
       </c>
       <c r="B563" s="2">
-        <v>3.4324170046113491</v>
+        <v>3.4590646668524241</v>
       </c>
       <c r="C563" s="2">
         <v>3</v>
@@ -5850,7 +5850,7 @@
         <v>45597</v>
       </c>
       <c r="B564" s="2">
-        <v>3.40756905449547</v>
+        <v>3.6410384065326813</v>
       </c>
       <c r="C564" s="2">
         <v>3</v>
@@ -5861,7 +5861,7 @@
         <v>45627</v>
       </c>
       <c r="B565" s="2">
-        <v>2.944720415032775</v>
+        <v>2.7039340078732357</v>
       </c>
       <c r="C565" s="2">
         <v>3</v>
@@ -5872,7 +5872,7 @@
         <v>45658</v>
       </c>
       <c r="B566" s="2">
-        <v>3.3958076650640714</v>
+        <v>3.4231271909300189</v>
       </c>
       <c r="C566" s="2">
         <v>3</v>
@@ -5883,7 +5883,7 @@
         <v>45689</v>
       </c>
       <c r="B567" s="2">
-        <v>3.6363679255675789</v>
+        <v>3.5272921754461302</v>
       </c>
       <c r="C567" s="2">
         <v>3</v>
@@ -5894,7 +5894,7 @@
         <v>45717</v>
       </c>
       <c r="B568" s="2">
-        <v>3.9863475756308953</v>
+        <v>3.9831015456860399</v>
       </c>
       <c r="C568" s="2">
         <v>3</v>
@@ -5905,11 +5905,95 @@
         <v>45748</v>
       </c>
       <c r="B569" s="2">
-        <v>4.2747750743596944</v>
+        <v>4.2582658023427165</v>
       </c>
       <c r="C569" s="2">
         <v>3</v>
       </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B570" s="2">
+        <v>4.4649512623073031</v>
+      </c>
+      <c r="C570" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B571" s="2">
+        <v>4.2879511965757038</v>
+      </c>
+      <c r="C571" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B572" s="2">
+        <v>4.3263721404429214</v>
+      </c>
+      <c r="C572" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B573" s="2">
+        <v>4.0367068626072315</v>
+      </c>
+      <c r="C573" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B574" s="2">
+        <v>4.2646168125829247</v>
+      </c>
+      <c r="C574" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B575" s="2">
+        <v>4.4766259127265542</v>
+      </c>
+      <c r="C575" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B576" s="2">
+        <v>3.7002971314932478</v>
+      </c>
+      <c r="C576" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B577" s="2"/>
+      <c r="C577" s="2"/>
     </row>
   </sheetData>
 </worksheet>
